--- a/data/trans_orig/P2A_fisi_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44368</t>
+          <t>44755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45301</t>
+          <t>46043</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93267</t>
+          <t>93234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98291</t>
+          <t>98293</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8437</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62967</t>
+          <t>62964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67306</t>
+          <t>67300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58717</t>
+          <t>59008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64302</t>
+          <t>64289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124383</t>
+          <t>124111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131018</t>
+          <t>130961</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63514</t>
+          <t>63550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128182</t>
+          <t>128643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>62072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69305</t>
+          <t>69340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134194</t>
+          <t>133450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138978</t>
+          <t>138987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47302</t>
+          <t>47804</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94078</t>
+          <t>93598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103712</t>
+          <t>104394</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109956</t>
+          <t>109959</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102360</t>
+          <t>101829</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>109147</t>
+          <t>109325</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209418</t>
+          <t>208981</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217958</t>
+          <t>217913</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84378</t>
+          <t>84246</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89536</t>
+          <t>89535</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85400</t>
+          <t>84856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93799</t>
+          <t>93109</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>171893</t>
+          <t>172283</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>181831</t>
+          <t>181880</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20139</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>488610</t>
+          <t>488329</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>498524</t>
+          <t>498347</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>502984</t>
+          <t>501929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>516721</t>
+          <t>516409</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>994541</t>
+          <t>995220</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1011769</t>
+          <t>1012360</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>23026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31090</t>
+          <t>31576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37194</t>
+          <t>37437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56210</t>
+          <t>55544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62218</t>
+          <t>62357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50928</t>
+          <t>51233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52498</t>
+          <t>51989</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57669</t>
+          <t>57664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105092</t>
+          <t>105227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>111988</t>
+          <t>111980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>47288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106529</t>
+          <t>106487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111909</t>
+          <t>111907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46150</t>
+          <t>46608</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49646</t>
+          <t>49641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>54810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98782</t>
+          <t>98228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104432</t>
+          <t>104451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37230</t>
+          <t>37600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38341</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43791</t>
+          <t>43813</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44604</t>
+          <t>44544</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85644</t>
+          <t>86067</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92222</t>
+          <t>92229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106728</t>
+          <t>107191</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114813</t>
+          <t>114757</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>115700</t>
+          <t>115452</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225346</t>
+          <t>225505</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>234830</t>
+          <t>234889</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>110321</t>
+          <t>110273</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114954</t>
+          <t>114958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>120979</t>
+          <t>120686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>128488</t>
+          <t>128373</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>234063</t>
+          <t>233906</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>242654</t>
+          <t>242644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>455637</t>
+          <t>456424</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>468548</t>
+          <t>468370</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>511064</t>
+          <t>511239</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>525422</t>
+          <t>526014</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>974114</t>
+          <t>973608</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>992114</t>
+          <t>991505</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40767</t>
+          <t>39971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44771</t>
+          <t>44763</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44609</t>
+          <t>44830</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50786</t>
+          <t>50796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87636</t>
+          <t>87415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94870</t>
+          <t>95112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8774</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62071</t>
+          <t>63510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74963</t>
+          <t>75764</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141923</t>
+          <t>141485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149974</t>
+          <t>149968</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44502</t>
+          <t>44510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43901</t>
+          <t>44535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86001</t>
+          <t>85405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92003</t>
+          <t>92002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30925</t>
+          <t>31729</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63061</t>
+          <t>62784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>23068</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27726</t>
+          <t>27602</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52810</t>
+          <t>52483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>58008</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109552</t>
+          <t>109305</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115997</t>
+          <t>115990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>109170</t>
+          <t>109608</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>117746</t>
+          <t>117763</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>222430</t>
+          <t>222549</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>232295</t>
+          <t>232371</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>121798</t>
+          <t>122033</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128419</t>
+          <t>128431</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>134301</t>
+          <t>134422</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>259617</t>
+          <t>258902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>266992</t>
+          <t>266831</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>504197</t>
+          <t>504204</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>517233</t>
+          <t>517137</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>552046</t>
+          <t>551223</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>563500</t>
+          <t>563716</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1059527</t>
+          <t>1059467</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69413</t>
+          <t>69976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70270</t>
+          <t>70629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77945</t>
+          <t>78064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142522</t>
+          <t>142794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150755</t>
+          <t>150639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23019</t>
+          <t>24010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113479</t>
+          <t>113602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125098</t>
+          <t>124687</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113678</t>
+          <t>113505</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124392</t>
+          <t>124546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232231</t>
+          <t>231240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>247872</t>
+          <t>247334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52948</t>
+          <t>52756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57754</t>
+          <t>57646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55878</t>
+          <t>56032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111312</t>
+          <t>110880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120295</t>
+          <t>120417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67242</t>
+          <t>67643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67706</t>
+          <t>67306</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77022</t>
+          <t>77102</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136411</t>
+          <t>138030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>146852</t>
+          <t>146927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30596</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34162</t>
+          <t>34151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>36778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69158</t>
+          <t>69829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74418</t>
+          <t>74523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>13032</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>37947</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44200</t>
+          <t>44085</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>51630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84520</t>
+          <t>84627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94542</t>
+          <t>95099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25237</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>36735</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106347</t>
+          <t>105686</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117600</t>
+          <t>117578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130775</t>
+          <t>128776</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>151421</t>
+          <t>151280</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>242382</t>
+          <t>243785</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>266065</t>
+          <t>266216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>121737</t>
+          <t>121385</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129113</t>
+          <t>129037</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>145532</t>
+          <t>144489</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154675</t>
+          <t>153945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>271142</t>
+          <t>270753</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>282209</t>
+          <t>282239</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44047</t>
+          <t>45360</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>34286</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62420</t>
+          <t>61958</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>63892</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100011</t>
+          <t>99037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>622108</t>
+          <t>620795</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>641375</t>
+          <t>639795</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>699552</t>
+          <t>700014</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>727002</t>
+          <t>727686</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1328116</t>
+          <t>1329090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1362555</t>
+          <t>1364235</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
